--- a/data/trans_camb/DC-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/DC-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 0,12</t>
+          <t>-7,47; 0,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -2,65</t>
+          <t>-10,06; -3,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,52</t>
+          <t>1,48; 10,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 8,64</t>
+          <t>-0,49; 8,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,45</t>
+          <t>-6,88; 1,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,69</t>
+          <t>6,15; 18,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,34</t>
+          <t>-2,47; 3,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -1,45</t>
+          <t>-7,08; -1,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 13,6</t>
+          <t>6,65; 13,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 0,77</t>
+          <t>-41,67; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -19,04</t>
+          <t>-54,81; -20,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 74,58</t>
+          <t>8,35; 75,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 43,27</t>
+          <t>-2,16; 46,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 7,58</t>
+          <t>-28,14; 9,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,99; 94,09</t>
+          <t>27,64; 92,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 19,12</t>
+          <t>-12,42; 20,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; -8,41</t>
+          <t>-34,93; -7,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 79,56</t>
+          <t>33,52; 80,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,24</t>
+          <t>-6,22; 0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -2,44</t>
+          <t>-8,71; -2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,9</t>
+          <t>-8,91; 5,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 0,14</t>
+          <t>-7,83; 0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -4,66</t>
+          <t>-12,27; -4,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 16,85</t>
+          <t>9,08; 17,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -1,06</t>
+          <t>-5,79; -0,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -4,42</t>
+          <t>-9,35; -4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 9,55</t>
+          <t>-3,64; 9,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 2,0</t>
+          <t>-37,52; 2,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,34; -19,02</t>
+          <t>-53,98; -22,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 43,44</t>
+          <t>-54,96; 41,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 0,74</t>
+          <t>-27,63; 1,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,24; -19,28</t>
+          <t>-44,45; -19,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,85; 72,18</t>
+          <t>31,05; 72,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -5,55</t>
+          <t>-27,22; -3,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -23,54</t>
+          <t>-43,86; -24,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 48,42</t>
+          <t>-17,37; 50,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -9,8</t>
+          <t>-17,95; -9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,99; -9,37</t>
+          <t>-16,77; -9,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 6,46</t>
+          <t>-3,19; 6,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -6,76</t>
+          <t>-16,53; -7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,8; -15,79</t>
+          <t>-24,51; -16,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 40,9</t>
+          <t>2,22; 41,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -9,7</t>
+          <t>-15,59; -9,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -14,06</t>
+          <t>-19,53; -13,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 31,49</t>
+          <t>1,92; 31,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,5; -50,55</t>
+          <t>-73,9; -50,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,76; -48,22</t>
+          <t>-71,06; -47,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 34,13</t>
+          <t>-13,09; 32,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,81; -20,34</t>
+          <t>-44,64; -21,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -49,82</t>
+          <t>-65,61; -49,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,53; 131,1</t>
+          <t>6,5; 128,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -35,95</t>
+          <t>-51,83; -34,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -52,65</t>
+          <t>-65,69; -52,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 113,47</t>
+          <t>6,83; 116,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -6,15</t>
+          <t>-12,43; -6,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -4,93</t>
+          <t>-11,28; -5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,27</t>
+          <t>0,57; 7,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -0,88</t>
+          <t>-8,41; -0,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,9; -3,45</t>
+          <t>-11,36; -3,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 24,59</t>
+          <t>6,5; 23,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -4,19</t>
+          <t>-9,16; -4,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -4,89</t>
+          <t>-10,13; -4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,98</t>
+          <t>4,97; 17,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,24; -35,13</t>
+          <t>-60,37; -35,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,91; -28,55</t>
+          <t>-55,03; -28,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 49,34</t>
+          <t>2,86; 45,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,72; -3,22</t>
+          <t>-27,08; -3,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -12,69</t>
+          <t>-36,06; -13,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,67; 85,69</t>
+          <t>21,16; 83,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -18,46</t>
+          <t>-36,3; -18,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -20,96</t>
+          <t>-40,04; -21,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,5; 68,77</t>
+          <t>19,4; 71,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -5,44</t>
+          <t>-8,89; -5,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -6,4</t>
+          <t>-9,89; -6,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,08</t>
+          <t>-1,78; 5,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -2,0</t>
+          <t>-6,31; -1,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -7,47</t>
+          <t>-11,43; -7,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 25,4</t>
+          <t>9,9; 25,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -4,23</t>
+          <t>-6,87; -4,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -7,44</t>
+          <t>-9,94; -7,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 16,15</t>
+          <t>5,57; 15,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -32,95</t>
+          <t>-47,94; -33,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -37,94</t>
+          <t>-53,01; -38,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 30,35</t>
+          <t>-9,21; 30,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -7,26</t>
+          <t>-21,42; -7,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -28,01</t>
+          <t>-39,49; -27,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,71; 93,93</t>
+          <t>35,05; 92,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -19,24</t>
+          <t>-29,2; -18,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,51; -33,46</t>
+          <t>-42,64; -33,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,99; 70,52</t>
+          <t>23,81; 65,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DC-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/DC-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>11,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,19</t>
+          <t>-7,36; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -3,0</t>
+          <t>-9,82; -2,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 10,41</t>
+          <t>1,32; 9,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,88</t>
+          <t>-0,4; 8,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 1,73</t>
+          <t>-7,1; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 18,25</t>
+          <t>12,02; 20,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,44</t>
+          <t>-2,82; 2,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -1,33</t>
+          <t>-7,37; -1,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 13,66</t>
+          <t>8,36; 14,22</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 1,33</t>
+          <t>-41,87; 0,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,81; -20,34</t>
+          <t>-54,71; -19,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 75,89</t>
+          <t>7,2; 68,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 46,12</t>
+          <t>-2,12; 45,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 9,26</t>
+          <t>-29,67; 9,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,64; 92,89</t>
+          <t>49,85; 110,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 20,03</t>
+          <t>-14,03; 16,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,93; -7,84</t>
+          <t>-35,47; -8,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,52; 80,65</t>
+          <t>40,82; 82,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,95</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>8,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,09</t>
+          <t>-6,11; 0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -2,84</t>
+          <t>-8,61; -2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 5,64</t>
+          <t>0,97; 8,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,3</t>
+          <t>-8,11; -0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -4,76</t>
+          <t>-12,41; -4,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 17,1</t>
+          <t>9,07; 16,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; -0,63</t>
+          <t>-5,96; -0,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -4,65</t>
+          <t>-9,72; -4,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 9,81</t>
+          <t>6,31; 11,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,52; 2,03</t>
+          <t>-37,08; 2,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,98; -22,68</t>
+          <t>-52,18; -20,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 41,45</t>
+          <t>5,57; 65,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 1,84</t>
+          <t>-28,61; -0,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,45; -19,97</t>
+          <t>-44,47; -20,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,05; 72,99</t>
+          <t>32,43; 72,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,22; -3,35</t>
+          <t>-27,11; -4,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,86; -24,89</t>
+          <t>-44,69; -24,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 50,34</t>
+          <t>28,64; 61,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -9,7</t>
+          <t>-17,74; -9,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -9,25</t>
+          <t>-16,82; -9,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 6,13</t>
+          <t>-2,85; 6,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -7,06</t>
+          <t>-16,05; -6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,51; -16,29</t>
+          <t>-24,97; -15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 41,28</t>
+          <t>1,89; 11,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -9,46</t>
+          <t>-15,64; -9,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,53; -13,85</t>
+          <t>-19,68; -13,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 31,25</t>
+          <t>1,09; 7,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,9; -50,52</t>
+          <t>-73,61; -51,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,06; -47,92</t>
+          <t>-70,1; -48,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 32,81</t>
+          <t>-12,16; 29,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,64; -21,39</t>
+          <t>-43,1; -21,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,61; -49,45</t>
+          <t>-66,19; -48,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 128,11</t>
+          <t>4,98; 35,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -34,95</t>
+          <t>-51,77; -35,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -52,02</t>
+          <t>-65,84; -51,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 116,69</t>
+          <t>3,47; 29,25</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,05</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,62</t>
+          <t>5,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -6,11</t>
+          <t>-12,44; -6,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -5,01</t>
+          <t>-11,28; -4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,8</t>
+          <t>-0,18; 6,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -0,89</t>
+          <t>-9,03; -1,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -3,59</t>
+          <t>-11,49; -3,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 23,79</t>
+          <t>4,37; 11,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -4,19</t>
+          <t>-9,56; -4,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -4,98</t>
+          <t>-10,06; -5,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 17,04</t>
+          <t>3,12; 8,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,37; -35,09</t>
+          <t>-60,57; -36,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -28,8</t>
+          <t>-54,62; -27,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 45,44</t>
+          <t>-1,05; 41,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,08; -3,27</t>
+          <t>-28,24; -3,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,06; -13,07</t>
+          <t>-36,68; -11,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,16; 83,18</t>
+          <t>13,75; 43,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,3; -18,07</t>
+          <t>-37,23; -19,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -21,76</t>
+          <t>-39,49; -22,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,4; 71,83</t>
+          <t>12,35; 38,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -5,59</t>
+          <t>-8,94; -5,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -6,41</t>
+          <t>-9,69; -6,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,15</t>
+          <t>1,93; 5,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,93</t>
+          <t>-6,32; -1,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -7,31</t>
+          <t>-11,56; -7,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,26</t>
+          <t>9,05; 13,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -4,06</t>
+          <t>-6,96; -4,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -7,31</t>
+          <t>-9,97; -7,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 15,07</t>
+          <t>6,15; 9,08</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -33,64</t>
+          <t>-48,6; -33,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -38,23</t>
+          <t>-52,57; -38,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 30,8</t>
+          <t>10,59; 34,77</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -7,26</t>
+          <t>-21,6; -7,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -27,42</t>
+          <t>-39,64; -27,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,05; 92,26</t>
+          <t>31,36; 48,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,2; -18,1</t>
+          <t>-29,47; -18,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -33,14</t>
+          <t>-42,53; -33,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>23,81; 65,41</t>
+          <t>26,1; 41,19</t>
         </is>
       </c>
     </row>
